--- a/GearSage-client/pkgGear/data_raw/daiwa_spinning_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_spinning_reels_import.xlsx
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25SALTIGA 8000-P</t>
+          <t>8000-P</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25SALTIGA 8000-H</t>
+          <t>8000-H</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25SALTIGA 10000-P</t>
+          <t>10000-P</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25SALTIGA 10000-H</t>
+          <t>10000-H</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25SALTIGA 14000-P</t>
+          <t>14000-P</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25SALTIGA 14000-XH</t>
+          <t>14000-XH</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25SALTIGA 18000-H</t>
+          <t>18000-H</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25SALTIGA 20000-P</t>
+          <t>20000-P</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25SALTIGA 20000-H</t>
+          <t>20000-H</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25SALTIGA 25000-P</t>
+          <t>25000-P</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25SALTIGA 30000-P</t>
+          <t>30000-P</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25SALTIGA 30000-H</t>
+          <t>30000-H</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23 SALTIGA 4000-H</t>
+          <t>4000-H</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23 SALTIGA 4000-XH</t>
+          <t>4000-XH</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23 SALTIGA 5000-P</t>
+          <t>5000-P</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23 SALTIGA 5000-H</t>
+          <t>5000-H</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23 SALTIGA 5000-XH</t>
+          <t>5000-XH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23 SALTIGA 6000-P</t>
+          <t>6000-P</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23 SALTIGA 6000-H</t>
+          <t>6000-H</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23 SALTIGA 6000-XH</t>
+          <t>6000-XH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22EXIST LT2000S-P</t>
+          <t>LT2000S-P</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22EXIST LT2000S-H</t>
+          <t>LT2000S-H</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22EXIST LT2500S</t>
+          <t>LT2500S</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22EXIST LT2500S-H</t>
+          <t>LT2500S-H</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22EXIST LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22EXIST LT2500S-DH</t>
+          <t>LT2500S-DH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22EXIST PC LT2500</t>
+          <t>PC LT2500</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>22EXIST PC LT2500-H</t>
+          <t>PC LT2500-H</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22EXIST LT3000S</t>
+          <t>LT3000S</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22EXIST LT3000-H</t>
+          <t>LT3000-H</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>22EXIST PC LT3000</t>
+          <t>PC LT3000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22EXIST PC LT3000-XH</t>
+          <t>PC LT3000-XH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>22EXIST LT4000</t>
+          <t>LT4000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>22EXIST LT4000-XH</t>
+          <t>LT4000-XH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22EXIST LT5000-C</t>
+          <t>LT5000-C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22EXIST LT5000-CXH</t>
+          <t>LT5000-CXH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22EXIST SF1000S-P</t>
+          <t>SF1000S-P</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22EXIST SF2000SS-P</t>
+          <t>SF2000SS-P</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>22EXIST SF2000SS-H</t>
+          <t>SF2000SS-H</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22EXIST SF2500SS</t>
+          <t>SF2500SS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>22EXIST SF2500SS-H</t>
+          <t>SF2500SS-H</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 8000-P</t>
+          <t>8000-P</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 8000-H</t>
+          <t>8000-H</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 10000-P</t>
+          <t>10000-P</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 10000-H</t>
+          <t>10000-H</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 14000-P</t>
+          <t>14000-P</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 14000-XH</t>
+          <t>14000-XH</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 18000-H</t>
+          <t>18000-H</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 20000-P</t>
+          <t>20000-P</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>26 CERTATE SW 20000-H</t>
+          <t>20000-H</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT3000-CH</t>
+          <t>LT3000-CH</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT3000</t>
+          <t>LT3000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT3000-XH</t>
+          <t>LT3000-XH</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT4000-C</t>
+          <t>LT4000-C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT4000-CXH</t>
+          <t>LT4000-CXH</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT5000D-CXH</t>
+          <t>LT5000D-CXH</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT5000D</t>
+          <t>LT5000D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>26 CERTATE HD LT5000D-XH</t>
+          <t>LT5000D-XH</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 4000-H</t>
+          <t>4000-H</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 4000-XH</t>
+          <t>4000-XH</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 5000-P</t>
+          <t>5000-P</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 5000-H</t>
+          <t>5000-H</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 5000-XH</t>
+          <t>5000-XH</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 6000-P</t>
+          <t>6000-P</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 6000-H</t>
+          <t>6000-H</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>24 CERTATE SW 6000-XH</t>
+          <t>6000-XH</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>21 Surf Basia 45 06PE</t>
+          <t>06PE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>21 Surf Basia 45 15 PE</t>
+          <t>15 PE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>21 Surf Basia 45QD for No</t>
+          <t>QD for No</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>23AIRITY LT2000S-P</t>
+          <t>LT2000S-P</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>23AIRITY LT2000S-H</t>
+          <t>LT2000S-H</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>23AIRITY LT2500S</t>
+          <t>LT2500S</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>23AIRITY LT2500S-DH</t>
+          <t>LT2500S-DH</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>23AIRITY LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>23AIRITY PC LT2500</t>
+          <t>PC LT2500</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>23AIRITY PC LT2500-H</t>
+          <t>PC LT2500-H</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>23AIRITY LT3000-H</t>
+          <t>LT3000-H</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>23AIRITY PC LT3000</t>
+          <t>PC LT3000</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>23AIRITY PC LT3000-XH</t>
+          <t>PC LT3000-XH</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>23AIRITY LT4000-XH</t>
+          <t>LT4000-XH</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14585,7 +14585,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>23AIRITY LT5000D-CXH</t>
+          <t>LT5000D-CXH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>23AIRITY SF1000S-P</t>
+          <t>SF1000S-P</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>23AIRITY SF2000SS-H</t>
+          <t>SF2000SS-H</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>23AIRITY SF2000SS-P</t>
+          <t>SF2000SS-P</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>23AIRITY SF2500SS</t>
+          <t>SF2500SS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>23AIRITY SF2500SS-H-QD</t>
+          <t>SF2500SS-H-QD</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>23AIRITY ST SF1000S-P</t>
+          <t>SF1000S-P</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>23AIRITY ST SF2000SS-P</t>
+          <t>SF2000SS-P</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>23AIRITY ST SF2000SS-H</t>
+          <t>SF2000SS-H</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>23AIRITY ST SF2500SS-H-QD</t>
+          <t>SF2500SS-H-QD</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -16060,7 +16060,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>23AIRITY ST LT2000S-P</t>
+          <t>LT2000S-P</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>23AIRITY ST LT2500S-XH-QD</t>
+          <t>LT2500S-XH-QD</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>24 CERTATE FC LT2000S-P</t>
+          <t>FC LT2000S-P</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>24 CERTATE FC LT2000S-H</t>
+          <t>FC LT2000S-H</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>24 CERTATE FC LT2500S</t>
+          <t>FC LT2500S</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>24 CERTATE FC LT2500S-XH</t>
+          <t>FC LT2500S-XH</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>24 CERTATE FC LT2500S-DH</t>
+          <t>FC LT2500S-DH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>24 CERTATE LT2500</t>
+          <t>LT2500</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>24 CERTATE LT2500-H</t>
+          <t>LT2500-H</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -17338,7 +17338,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>24 CERTATE LT3000-CH</t>
+          <t>LT3000-CH</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>24 CERTATE LT3000</t>
+          <t>LT3000</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>24 CERTATE LT3000-XH</t>
+          <t>LT3000-XH</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>24 CERTATE LT4000-C</t>
+          <t>LT4000-C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17896,7 +17896,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>24 CERTATE LT4000-CXH</t>
+          <t>LT4000-CXH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>24 CERTATE LT5000D-CXH</t>
+          <t>LT5000D-CXH</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>24 CERTATE LT5000D</t>
+          <t>LT5000D</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>24 CERTATE LT5000D-XH</t>
+          <t>LT5000D-XH</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>25EMERALDAS AIR LT2500S</t>
+          <t>LT2500S</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>25EMERALDAS AIR LT2500S-DH</t>
+          <t>LT2500S-DH</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>25EMERALDAS AIR PC LT2500-DH</t>
+          <t>PC LT2500-DH</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>25EMERALDAS AIR PC LT2500-H</t>
+          <t>PC LT2500-H</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>24LUVIAS LT2000S-P</t>
+          <t>LT2000S-P</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>24LUVIAS LT2000S-H</t>
+          <t>LT2000S-H</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>24LUVIAS LT2500S</t>
+          <t>LT2500S</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>24LUVIAS LT2500S-DH</t>
+          <t>LT2500S-DH</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19470,7 +19470,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>24LUVIAS LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>24LUVIAS PC LT2500</t>
+          <t>PC LT2500</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>24LUVIAS PC LT2500-H</t>
+          <t>PC LT2500-H</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19866,7 +19866,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>24LUVIAS LT3000-H</t>
+          <t>LT3000-H</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19998,7 +19998,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>24LUVIAS PC LT3000</t>
+          <t>PC LT3000</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>24LUVIAS PC LT3000-XH</t>
+          <t>PC LT3000-XH</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>24LUVIAS LT4000-XH</t>
+          <t>LT4000-XH</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>24LUVIAS LT5000D-CXH</t>
+          <t>LT5000D-CXH</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>24LUVIAS SF2000SS-P</t>
+          <t>SF2000SS-P</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>24LUVIAS SF2000SS-H</t>
+          <t>SF2000SS-H</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>24LUVIAS SF2500SS</t>
+          <t>SF2500SS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>24LUVIAS SF2500SS-H</t>
+          <t>SF2500SS-H</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>22CALDIA SW 4000-CXH</t>
+          <t>4000-CXH</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>22CALDIA SW 4000D-CXH</t>
+          <t>4000D-CXH</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21323,7 +21323,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>22CALDIA SW 5000-CXH</t>
+          <t>5000-CXH</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21455,7 +21455,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>22CALDIA SW 5000D-CXH</t>
+          <t>5000D-CXH</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>22CALDIA SW 6000S-H</t>
+          <t>6000S-H</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>22CALDIA SW 6000D-H</t>
+          <t>6000D-H</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>22CALDIA SW 8000-P</t>
+          <t>8000-P</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>22CALDIA SW 8000-H</t>
+          <t>8000-H</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22115,7 +22115,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>22CALDIA SW 10000-P</t>
+          <t>10000-P</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22247,7 +22247,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>22CALDIA SW 10000-H</t>
+          <t>10000-H</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>22CALDIA SW 14000-H</t>
+          <t>14000-H</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22511,7 +22511,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>22CALDIA SW 18000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>24LUVIAS ST SF1000S-P</t>
+          <t>SF1000S-P</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>24LUVIAS ST SF2000SS-P</t>
+          <t>SF2000SS-P</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>24LUVIAS ST SF2000SS-H</t>
+          <t>SF2000SS-H</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>24LUVIAS ST SF2500SS-H</t>
+          <t>SF2500SS-H</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>24LUVIAS ST LT2000S-P</t>
+          <t>LT2000S-P</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>24LUVIAS ST LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -23435,7 +23435,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LONGBEAM 35 06PE</t>
+          <t>06PE</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LONGBEAM 35 QD 5</t>
+          <t>QD 5</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LONGBEAM 35 QD 12</t>
+          <t>QD 12</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>25CALDIA FC LT1000S</t>
+          <t>FC LT1000S</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -23963,7 +23963,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>25CALDIA FC LT2000S</t>
+          <t>FC LT2000S</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>25CALDIA FC LT2000S-H</t>
+          <t>FC LT2000S-H</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -24237,7 +24237,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>25CALDIA FC LT2500S</t>
+          <t>FC LT2500S</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>25CALDIA FC LT2500S-H</t>
+          <t>FC LT2500S-H</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -24511,7 +24511,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>25CALDIA LT2500</t>
+          <t>LT2500</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>25CALDIA LT2500S</t>
+          <t>LT2500S</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -24775,7 +24775,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>25CALDIA LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -24907,7 +24907,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>25CALDIA LT3000S-CXH</t>
+          <t>LT3000S-CXH</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -25044,7 +25044,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>25CALDIA LT3000</t>
+          <t>LT3000</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>25CALDIA LT3000-XH</t>
+          <t>LT3000-XH</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>25CALDIA LT4000-C</t>
+          <t>LT4000-C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>25CALDIA LT4000-CXH</t>
+          <t>LT4000-CXH</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>25CALDIA LT5000-C</t>
+          <t>LT5000-C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>25CALDIA LT5000-CXH</t>
+          <t>LT5000-CXH</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -25856,7 +25856,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>18 Power Surf SS 3500QD</t>
+          <t>3500QD</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>18 Power Surf SS 4000QD</t>
+          <t>4000QD</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>18 Power Surf SS 4500QD</t>
+          <t>4500QD</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -26267,7 +26267,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>18 Power Surf SS 5000QD</t>
+          <t>5000QD</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>23 月下美人 LT1000S</t>
+          <t>LT1000S</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>23 月下美人 LT2000S</t>
+          <t>LT2000S</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>23 月下美人 LT2000S-H</t>
+          <t>LT2000S-H</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>23TATULA FC LT2500SS-QD</t>
+          <t>FC LT2500SS-QD</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -26952,7 +26952,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>23TATULA FC LT2500SS-H-QD</t>
+          <t>FC LT2500SS-H-QD</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>23TATULA LT2500S-XH-QD</t>
+          <t>LT2500S-XH-QD</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>23BG SW 4000D-CXH</t>
+          <t>4000D-CXH</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -27383,7 +27383,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>23BG SW 5000D-CXH</t>
+          <t>5000D-CXH</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>23BG SW 6000D-P</t>
+          <t>6000D-P</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -27647,7 +27647,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>23BG SW 6000D-H</t>
+          <t>6000D-H</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>23BG SW 8000-P</t>
+          <t>8000-P</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -27911,7 +27911,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>23BG SW 8000-H</t>
+          <t>8000-H</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>23BG SW 10000-H</t>
+          <t>10000-H</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>23BG SW 14000-H</t>
+          <t>14000-H</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>23BG SW 18000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -28439,7 +28439,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>23LEXA LT2500</t>
+          <t>LT2500</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -28576,7 +28576,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>23LEXA LT2500S</t>
+          <t>LT2500S</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>23LEXA LT2500-XH</t>
+          <t>LT2500-XH</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -28850,7 +28850,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>23LEXA LT3000S-C</t>
+          <t>LT3000S-C</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -28992,7 +28992,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>23LEXA LT3000S-CXH</t>
+          <t>LT3000S-CXH</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>23LEXA LT3000</t>
+          <t>LT3000</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>23LEXA LT3000-XH</t>
+          <t>LT3000-XH</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -29408,7 +29408,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>23LEXA LT4000-C</t>
+          <t>LT4000-C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -29550,7 +29550,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>23LEXA LT4000-CXH</t>
+          <t>LT4000-CXH</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -29692,7 +29692,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>23LEXA LT5000-C</t>
+          <t>LT5000-C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>23LEXA LT5000-CXH</t>
+          <t>LT5000-CXH</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>23LEXA LT6000D-H</t>
+          <t>LT6000D-H</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -30113,7 +30113,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>26FREAMS LT1000S-P</t>
+          <t>LT1000S-P</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -30250,7 +30250,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>26FREAMS LT2000S-P</t>
+          <t>LT2000S-P</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -30387,7 +30387,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>26FREAMS LT2000S-XH</t>
+          <t>LT2000S-XH</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -30524,7 +30524,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>26FREAMS LT2500D</t>
+          <t>LT2500D</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -30661,7 +30661,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>26FREAMS LT2500</t>
+          <t>LT2500</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -30798,7 +30798,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>26FREAMS LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>26FREAMS LT3000D-C</t>
+          <t>LT3000D-C</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>26FREAMS LT3000-CXH</t>
+          <t>LT3000-CXH</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>26FREAMS LT4000-C</t>
+          <t>LT4000-C</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -31361,7 +31361,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>26FREAMS LT4000-CXH</t>
+          <t>LT4000-CXH</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -31503,7 +31503,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>26FREAMS LT5000D-CXH</t>
+          <t>LT5000D-CXH</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -31645,7 +31645,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>26FREAMS LT6000D-H</t>
+          <t>LT6000D-H</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -31782,7 +31782,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>24 EMERALDAS X LT2500</t>
+          <t>LT2500</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -31909,7 +31909,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>24 EMERALDAS X LT2500-XH</t>
+          <t>LT2500-XH</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>24 EMERALDAS X LT2500-DH</t>
+          <t>LT2500-DH</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -32163,7 +32163,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>24 EMERALDAS X LT2500-XH-DH</t>
+          <t>LT2500-XH-DH</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -32290,7 +32290,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>17WINDSURF35 細線</t>
+          <t>細線</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -32422,7 +32422,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>17WINDSURF35 粗紗</t>
+          <t>粗紗</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -32554,7 +32554,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>26 AORIMATIC BR LT3000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>26 AORIMATIC BR LT3000D</t>
+          <t>3000D</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>17 CROSSCAST 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>17 CROSSCAST 4500</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>17 CROSSCAST 5000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>17 CROSSCAST 5500</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -33381,7 +33381,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>17 CROSSCAST 6000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -33513,7 +33513,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>17 CROSSCAST 4000QD</t>
+          <t>4000QD</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -33645,7 +33645,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>24 REVROS LT1000S</t>
+          <t>LT1000S</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>24 REVROS LT2000S</t>
+          <t>LT2000S</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -33939,7 +33939,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>24 REVROS LT2000S-XH</t>
+          <t>LT2000S-XH</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -34086,7 +34086,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>24 REVROS LT2500D</t>
+          <t>LT2500D</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -34233,7 +34233,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>24 REVROS LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>24 REVROS LT2500S-DH</t>
+          <t>LT2500S-DH</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -34527,7 +34527,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>24 REVROS LT3000D-C</t>
+          <t>LT3000D-C</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -34679,7 +34679,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>24 REVROS LT3000-CXH</t>
+          <t>LT3000-CXH</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>24 REVROS LT4000-CXH</t>
+          <t>LT4000-CXH</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -34983,7 +34983,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>24 REVROS LT5000-CXH</t>
+          <t>LT5000-CXH</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>24 REVROS LT6000D-H</t>
+          <t>LT6000D-H</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>17 FINESURF 35 細糸</t>
+          <t>細糸</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -35419,7 +35419,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>17 FINESURF 35 太糸</t>
+          <t>太糸</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -35556,7 +35556,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>20 CREST LT2000</t>
+          <t>LT2000</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -35698,7 +35698,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>20 CREST LT2000S</t>
+          <t>LT2000S</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -35840,7 +35840,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>20 CREST LT2500</t>
+          <t>LT2500</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -35982,7 +35982,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>20 CREST LT2500S</t>
+          <t>LT2500S</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>20 CREST LT2500S-XH</t>
+          <t>LT2500S-XH</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -36266,7 +36266,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>20 CREST LT3000-C</t>
+          <t>LT3000-C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>20 CREST LT3000-CXH</t>
+          <t>LT3000-CXH</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>20 CREST LT4000-C</t>
+          <t>LT4000-C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -36707,7 +36707,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>20 CREST LT4000-CXH</t>
+          <t>LT4000-CXH</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -36854,7 +36854,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>20 CREST LT5000-C</t>
+          <t>LT5000-C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>20 CREST LT5000-CXH</t>
+          <t>LT5000-CXH</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>20 CREST LT6000-H</t>
+          <t>LT6000-H</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -37290,7 +37290,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>MR1000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -37422,7 +37422,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>19MR 750</t>
+          <t>750</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -37554,7 +37554,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>16 REGAL 2004H 附PE線</t>
+          <t>2004H</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -37686,7 +37686,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>16 REGAL 2506H-DH 附PE線</t>
+          <t>2506H-DH</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -37818,7 +37818,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>16 REGAL 2508H 附PE線</t>
+          <t>2508H</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>16 REGAL 3000H 附PE線</t>
+          <t>3000H</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -38082,7 +38082,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>TAMAN MONSTER 6000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN 1500</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -38336,7 +38336,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN 2000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -38468,7 +38468,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN 2500</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN 3000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN 3500</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -38864,7 +38864,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN 4000</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -38996,7 +38996,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN CF 2000</t>
+          <t>CF 2000</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -39128,7 +39128,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN CF 2500</t>
+          <t>CF 2500</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -39260,7 +39260,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>17 WORLD SPIN CF 3000</t>
+          <t>CF 3000</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">

--- a/GearSage-client/pkgGear/data_raw/daiwa_spinning_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_spinning_reels_import.xlsx
@@ -1,36 +1,377 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24280" windowHeight="12940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="reel" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="spinning_reel_detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spinning_reel_detail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -38,15 +379,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
@@ -436,7 +1068,6 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -447,7 +1078,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
+  <cols>
+    <col width="52.7142857142857" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1225,9 +1859,9 @@
           <t>spinning</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/Airity%20ST_main.jpg</t>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/AIRITY%20ST_main.jpg</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3172,6 +3806,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" tooltip="https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/AIRITY%ST_main.jpg" display="https://static.gearsage.club/gearsage/Gearimg/images/daiwa_reels/AIRITY%ST_main.jpg" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3183,7 +3820,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AR262"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
